--- a/3x VCO/Outputs/BOM/3x VCO_BOM.xlsx
+++ b/3x VCO/Outputs/BOM/3x VCO_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jakub\Desktop\Eurorack-project\3x VCO\Outputs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2FD7090-98B3-4AF7-96A3-F4BD3ECD879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE6552D7-69EB-4D0A-AB40-FCC12A48D247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="3705" windowWidth="28800" windowHeight="15435" xr2:uid="{6BEA04E2-87CB-4F26-96CC-38C3B8E086A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{9AD9503C-A11F-40C1-8342-1B220F7B7823}"/>
   </bookViews>
   <sheets>
     <sheet name="3x VCO_BOM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>Quantity</t>
   </si>
@@ -71,21 +71,24 @@
     <t>Capacitor Electr THT 5mm</t>
   </si>
   <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>C4, C11</t>
+  </si>
+  <si>
+    <t>Capacitor THT 5mm</t>
+  </si>
+  <si>
+    <t>2,2nF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
     <t>1uF</t>
   </si>
   <si>
-    <t>C4, C11</t>
-  </si>
-  <si>
-    <t>Capacitor THT 5mm</t>
-  </si>
-  <si>
-    <t>2,2nF</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
     <t>C1, C3</t>
   </si>
   <si>
@@ -173,16 +176,16 @@
     <t>R7</t>
   </si>
   <si>
+    <t>1Meg</t>
+  </si>
+  <si>
+    <t>R8, R9</t>
+  </si>
+  <si>
     <t>47k</t>
   </si>
   <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>1Meg</t>
-  </si>
-  <si>
-    <t>R8, R9</t>
+    <t>R6, R26</t>
   </si>
   <si>
     <t>68k</t>
@@ -203,7 +206,7 @@
     <t>100k</t>
   </si>
   <si>
-    <t>R2, R3, R4, R5, R14, R16, R17, R18, R19, R20</t>
+    <t>R2, R3, R4, R5, R14, R16, R17, R18, R19, R20, R27</t>
   </si>
   <si>
     <t>Schottky Diode THT</t>
@@ -642,7 +645,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3941F0-67EF-4887-8D86-C9373AB3F9F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA82E783-6BC6-4D20-8EEA-65821BC8D522}">
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -732,11 +735,11 @@
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -747,11 +750,11 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -759,12 +762,12 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -772,14 +775,14 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -787,12 +790,12 @@
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -800,12 +803,12 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -813,12 +816,12 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -826,14 +829,14 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -841,14 +844,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -856,14 +859,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -871,14 +874,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -886,14 +889,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -901,29 +904,29 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -931,14 +934,14 @@
         <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -946,14 +949,14 @@
         <v>2</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -961,14 +964,14 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -976,29 +979,29 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1006,14 +1009,14 @@
         <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1021,14 +1024,14 @@
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1036,12 +1039,12 @@
         <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1049,14 +1052,14 @@
         <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1064,14 +1067,14 @@
         <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1079,14 +1082,14 @@
         <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
